--- a/format-smoke.xlsx
+++ b/format-smoke.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Desktop\excel-ai-addin-rc6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{570B7F34-49B5-415D-8080-44E9EFB0A20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B0633D-3E52-4658-B3AF-51DA26DD0A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -972,7 +972,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="604" row="3">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1138,8 +1138,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
